--- a/jogos_2025-06-02.xlsx
+++ b/jogos_2025-06-02.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -205,15 +151,12 @@
     <t>Paraguay Division Profesional</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
+    <t>Argentina Prim B Nacional</t>
   </si>
   <si>
     <t>Chile Primera División</t>
   </si>
   <si>
-    <t>Argentina Prim B Nacional</t>
-  </si>
-  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
@@ -223,24 +166,18 @@
     <t>2025</t>
   </si>
   <si>
-    <t>2024/2025</t>
-  </si>
-  <si>
     <t>Valur</t>
   </si>
   <si>
     <t>Sportivo Luqueño</t>
   </si>
   <si>
-    <t>CS Constantine</t>
+    <t>Nueva Chicago</t>
   </si>
   <si>
     <t>Cobresal</t>
   </si>
   <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
     <t>Chapecoense</t>
   </si>
   <si>
@@ -259,15 +196,12 @@
     <t>Sportivo Ameliano</t>
   </si>
   <si>
-    <t>USM Khenchela</t>
+    <t>Temperley</t>
   </si>
   <si>
     <t>Deportes Iquique</t>
   </si>
   <si>
-    <t>Temperley</t>
-  </si>
-  <si>
     <t>Amazonas</t>
   </si>
   <si>
@@ -280,10 +214,40 @@
     <t>Criciúma</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['50', '68']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['45+5', '77']</t>
+  </si>
+  <si>
+    <t>['15', '27', '57', '90+3']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['64']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['78']</t>
+  </si>
+  <si>
+    <t>['19', '27', '65']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['52']</t>
   </si>
 </sst>
 </file>
@@ -647,10 +611,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD10"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,85 +729,31 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45810</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -852,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -864,49 +774,49 @@
         <v>6</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD2">
         <v>1.83</v>
@@ -915,99 +825,45 @@
         <v>1.8</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ2" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="AK2" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>0</v>
-      </c>
-      <c r="BC2">
-        <v>0</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45810.67708333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45810</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1022,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L3">
         <v>2.82</v>
@@ -1043,34 +899,34 @@
         <v>1.95</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S3">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V3">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA3">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AB3">
         <v>2.25</v>
@@ -1079,111 +935,57 @@
         <v>1.53</v>
       </c>
       <c r="AD3">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AI3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="AK3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL3">
-        <v>1.36</v>
-      </c>
-      <c r="AM3">
-        <v>1.32</v>
-      </c>
-      <c r="AN3">
-        <v>1.36</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>1.5</v>
-      </c>
-      <c r="AQ3">
-        <v>1.7</v>
-      </c>
-      <c r="AR3">
-        <v>2.7</v>
-      </c>
-      <c r="AS3">
-        <v>3</v>
-      </c>
-      <c r="AT3">
-        <v>4.05</v>
-      </c>
-      <c r="AU3">
-        <v>2.63</v>
-      </c>
-      <c r="AV3">
-        <v>1.91</v>
-      </c>
-      <c r="AW3">
-        <v>1.57</v>
-      </c>
-      <c r="AX3">
-        <v>1.33</v>
-      </c>
-      <c r="AY3">
-        <v>1.22</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.25</v>
-      </c>
-      <c r="BC3">
-        <v>1.95</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>68</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45810.70833333334</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45810</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1192,177 +994,123 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="AK4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>73</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45810.79166666666</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45810</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L5">
         <v>1.82</v>
@@ -1437,475 +1185,313 @@
         <v>1.1</v>
       </c>
       <c r="AJ5" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="AK5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL5">
-        <v>1.23</v>
-      </c>
-      <c r="AM5">
-        <v>1.26</v>
-      </c>
-      <c r="AN5">
-        <v>1.95</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>1.32</v>
-      </c>
-      <c r="AQ5">
-        <v>1.54</v>
-      </c>
-      <c r="AR5">
-        <v>1.88</v>
-      </c>
-      <c r="AS5">
-        <v>2.38</v>
-      </c>
-      <c r="AT5">
-        <v>3.05</v>
-      </c>
-      <c r="AU5">
-        <v>2.95</v>
-      </c>
-      <c r="AV5">
-        <v>2.23</v>
-      </c>
-      <c r="AW5">
-        <v>1.77</v>
-      </c>
-      <c r="AX5">
-        <v>1.47</v>
-      </c>
-      <c r="AY5">
-        <v>1.3</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.58</v>
-      </c>
-      <c r="BC5">
-        <v>2.51</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>74</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45810.79166666666</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45810</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L6">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="M6">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>4.75</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="P6">
-        <v>5.15</v>
+        <v>7.5</v>
       </c>
       <c r="Q6">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
-        <v>4.2</v>
+        <v>3.43</v>
       </c>
       <c r="U6">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="V6">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>4.8</v>
+        <v>6.37</v>
       </c>
       <c r="Z6">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AA6">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="AB6">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="AC6">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="AD6">
-        <v>7.1</v>
+        <v>3.8</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AF6">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="AG6">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AH6">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AI6">
         <v>1.02</v>
       </c>
       <c r="AJ6" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL6">
-        <v>1.48</v>
-      </c>
-      <c r="AM6">
-        <v>1.41</v>
-      </c>
-      <c r="AN6">
-        <v>1.44</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>1.49</v>
-      </c>
-      <c r="AQ6">
-        <v>1.89</v>
-      </c>
-      <c r="AR6">
-        <v>2.49</v>
-      </c>
-      <c r="AS6">
-        <v>3.4</v>
-      </c>
-      <c r="AT6">
-        <v>4.6</v>
-      </c>
-      <c r="AU6">
-        <v>2.3</v>
-      </c>
-      <c r="AV6">
-        <v>1.77</v>
-      </c>
-      <c r="AW6">
-        <v>1.42</v>
-      </c>
-      <c r="AX6">
-        <v>1.25</v>
-      </c>
-      <c r="AY6">
-        <v>1.15</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2</v>
-      </c>
-      <c r="BC6">
-        <v>2.4</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>68</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45810.79166666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45810</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
         <v>66</v>
       </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>88</v>
-      </c>
       <c r="L7">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="M7">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="N7">
-        <v>3.47</v>
+        <v>4.33</v>
       </c>
       <c r="O7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="P7">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q7">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AA7">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="AB7">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
         <v>1.48</v>
       </c>
       <c r="AD7">
-        <v>3.88</v>
+        <v>4.6</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG7">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AH7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AI7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="AK7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL7">
-        <v>1.35</v>
-      </c>
-      <c r="AM7">
-        <v>1.31</v>
-      </c>
-      <c r="AN7">
-        <v>1.73</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.23</v>
-      </c>
-      <c r="AQ7">
-        <v>1.28</v>
-      </c>
-      <c r="AR7">
-        <v>1.74</v>
-      </c>
-      <c r="AS7">
-        <v>1.97</v>
-      </c>
-      <c r="AT7">
-        <v>2.55</v>
-      </c>
-      <c r="AU7">
-        <v>3.65</v>
-      </c>
-      <c r="AV7">
-        <v>2.65</v>
-      </c>
-      <c r="AW7">
-        <v>2.29</v>
-      </c>
-      <c r="AX7">
-        <v>1.83</v>
-      </c>
-      <c r="AY7">
-        <v>1.45</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.67</v>
-      </c>
-      <c r="BC7">
-        <v>2.6</v>
-      </c>
-      <c r="BD7" s="3">
-        <v>45810.79166666666</v>
+        <v>75</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>45810.8125</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45810</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="L8">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="M8">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="N8">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="P8">
         <v>6.75</v>
       </c>
       <c r="Q8">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T8">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U8">
         <v>1.3</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W8">
         <v>1.04</v>
@@ -1914,439 +1500,161 @@
         <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AA8">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC8">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AD8">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AE8">
         <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AH8">
-        <v>8.75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ8" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="AK8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL8">
-        <v>1.33</v>
-      </c>
-      <c r="AM8">
-        <v>1.33</v>
-      </c>
-      <c r="AN8">
-        <v>1.88</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.68</v>
-      </c>
-      <c r="BC8">
-        <v>2.65</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>76</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45810.8125</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45810</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>2.02</v>
+      </c>
+      <c r="M9">
+        <v>3.15</v>
+      </c>
+      <c r="N9">
+        <v>3.25</v>
+      </c>
+      <c r="O9">
+        <v>1.73</v>
+      </c>
+      <c r="P9">
+        <v>6.5</v>
+      </c>
+      <c r="Q9">
+        <v>2.5</v>
+      </c>
+      <c r="R9">
+        <v>1.55</v>
+      </c>
+      <c r="S9">
+        <v>2.25</v>
+      </c>
+      <c r="T9">
+        <v>3.5</v>
+      </c>
+      <c r="U9">
+        <v>1.22</v>
+      </c>
+      <c r="V9">
+        <v>9</v>
+      </c>
+      <c r="W9">
+        <v>1.02</v>
+      </c>
+      <c r="X9">
+        <v>1.08</v>
+      </c>
+      <c r="Y9">
+        <v>5.7</v>
+      </c>
+      <c r="Z9">
+        <v>1.45</v>
+      </c>
+      <c r="AA9">
+        <v>2.37</v>
+      </c>
+      <c r="AB9">
+        <v>2.78</v>
+      </c>
+      <c r="AC9">
+        <v>1.42</v>
+      </c>
+      <c r="AD9">
+        <v>4.9</v>
+      </c>
+      <c r="AE9">
+        <v>1.13</v>
+      </c>
+      <c r="AF9">
+        <v>2.23</v>
+      </c>
+      <c r="AG9">
+        <v>1.68</v>
+      </c>
+      <c r="AH9">
+        <v>10.5</v>
+      </c>
+      <c r="AI9">
+        <v>1.04</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>68</v>
       </c>
-      <c r="E9" t="s">
+      <c r="AK9" t="s">
         <v>77</v>
       </c>
-      <c r="F9" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
-        <v>88</v>
-      </c>
-      <c r="L9">
-        <v>1.73</v>
-      </c>
-      <c r="M9">
-        <v>3.25</v>
-      </c>
-      <c r="N9">
-        <v>4.3</v>
-      </c>
-      <c r="O9">
-        <v>1.44</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>3.5</v>
-      </c>
-      <c r="R9">
-        <v>1.5</v>
-      </c>
-      <c r="S9">
-        <v>2.5</v>
-      </c>
-      <c r="T9">
-        <v>3.4</v>
-      </c>
-      <c r="U9">
-        <v>1.3</v>
-      </c>
-      <c r="V9">
-        <v>8</v>
-      </c>
-      <c r="W9">
-        <v>1.06</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>2.1</v>
-      </c>
-      <c r="AC9">
-        <v>1.61</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>2.38</v>
-      </c>
-      <c r="AG9">
-        <v>1.53</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AI9">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.44</v>
-      </c>
-      <c r="BC9">
-        <v>3.5</v>
-      </c>
-      <c r="BD9" s="3">
-        <v>45810.8125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:56">
-      <c r="A10" s="2">
-        <v>45810</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10">
-        <v>2.25</v>
-      </c>
-      <c r="M10">
-        <v>2.81</v>
-      </c>
-      <c r="N10">
-        <v>3.14</v>
-      </c>
-      <c r="O10">
-        <v>1.73</v>
-      </c>
-      <c r="P10">
-        <v>6.5</v>
-      </c>
-      <c r="Q10">
-        <v>2.5</v>
-      </c>
-      <c r="R10">
-        <v>1.5</v>
-      </c>
-      <c r="S10">
-        <v>2.4</v>
-      </c>
-      <c r="T10">
-        <v>3.34</v>
-      </c>
-      <c r="U10">
-        <v>1.29</v>
-      </c>
-      <c r="V10">
-        <v>10</v>
-      </c>
-      <c r="W10">
-        <v>1.03</v>
-      </c>
-      <c r="X10">
-        <v>1.06</v>
-      </c>
-      <c r="Y10">
-        <v>6.82</v>
-      </c>
-      <c r="Z10">
-        <v>1.43</v>
-      </c>
-      <c r="AA10">
-        <v>2.47</v>
-      </c>
-      <c r="AB10">
-        <v>2.25</v>
-      </c>
-      <c r="AC10">
-        <v>1.53</v>
-      </c>
-      <c r="AD10">
-        <v>4.75</v>
-      </c>
-      <c r="AE10">
-        <v>1.17</v>
-      </c>
-      <c r="AF10">
-        <v>1.98</v>
-      </c>
-      <c r="AG10">
-        <v>1.75</v>
-      </c>
-      <c r="AH10">
-        <v>9.5</v>
-      </c>
-      <c r="AI10">
-        <v>1.03</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AK10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AL10">
-        <v>1.36</v>
-      </c>
-      <c r="AM10">
-        <v>1.34</v>
-      </c>
-      <c r="AN10">
-        <v>1.59</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>1.16</v>
-      </c>
-      <c r="AQ10">
-        <v>1.33</v>
-      </c>
-      <c r="AR10">
-        <v>1.67</v>
-      </c>
-      <c r="AS10">
-        <v>1.87</v>
-      </c>
-      <c r="AT10">
-        <v>2.3</v>
-      </c>
-      <c r="AU10">
-        <v>4.35</v>
-      </c>
-      <c r="AV10">
-        <v>3.07</v>
-      </c>
-      <c r="AW10">
-        <v>2.33</v>
-      </c>
-      <c r="AX10">
-        <v>1.87</v>
-      </c>
-      <c r="AY10">
-        <v>1.53</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.73</v>
-      </c>
-      <c r="BC10">
-        <v>2.5</v>
-      </c>
-      <c r="BD10" s="3">
+      <c r="AL9" s="3">
         <v>45810.875</v>
       </c>
     </row>

--- a/jogos_2025-06-02.xlsx
+++ b/jogos_2025-06-02.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,23 +901,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="M4" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.32</v>
       </c>
-      <c r="S4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.46</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="X4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3.8</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['45+5', '77']</t>
+          <t>['15', '27', '57', '90+3']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45810.79166666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.75</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.24</v>
-      </c>
       <c r="Z6" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['15', '27', '57', '90+3']</t>
+          <t>['45+5', '77']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45810.79166666666</v>
